--- a/data/qkata.xlsx
+++ b/data/qkata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Κεντρική Επιτροπή Διαιτησίας\ΣΕΜΙΝΑΡΙΑ-ΕΞΕΤΑΣΕΙΣ\2026\WKF EXAMINATIONS 2026\ΕΦΑΡΜΟΓΗ Claude.ai\Quiz app\karate-tf-app\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Κεντρική Επιτροπή Διαιτησίας\ΣΕΜΙΝΑΡΙΑ-ΕΞΕΤΑΣΕΙΣ\2026\WKF EXAMINATIONS 2026\ΕΦΑΡΜΟΓΗ Claude.ai\mermaid app\App-2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5867728F-BB8A-450D-8657-F2D590BD5742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFF1E6F2-D137-4095-B2AC-505D11980714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25080" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026-v.2 (2)" sheetId="4" r:id="rId1"/>
@@ -2258,7 +2258,7 @@
         <v>116</v>
       </c>
       <c r="C120" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D120" s="3"/>
     </row>
